--- a/SGC-CKN/Excel/66fe416a-c8c6-4c23-acbc-7d7760f43499_Cọc_khoan_nhồi_-_Trụ_HN_P479_C7-P479_D2000_11-03-2026.xlsx
+++ b/SGC-CKN/Excel/66fe416a-c8c6-4c23-acbc-7d7760f43499_Cọc_khoan_nhồi_-_Trụ_HN_P479_C7-P479_D2000_11-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>C7-P479</t>
+    <t>C7</t>
   </si>
   <si>
     <t>Biên bản số</t>
